--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -46,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -54,13 +57,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -429,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -440,27 +452,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Precio</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Moneda</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Ultima_Actualizacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Fecha_Ejecucion</t>
         </is>
@@ -472,7 +484,7 @@
           <t>NATURAL_GAS_GBP</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="3" t="n">
         <v>12.271</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -497,7 +509,7 @@
           <t>BRENT_CRUDE_USD</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="3" t="n">
         <v>110.53</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -522,7 +534,7 @@
           <t>JKM_LNG_USD</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="3" t="n">
         <v>18.96</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -547,7 +559,7 @@
           <t>EU_CARBON_EUR</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="3" t="n">
         <v>74.53</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -572,7 +584,7 @@
           <t>NATURAL_GAS_GBP</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="3" t="n">
         <v>11.847</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -597,7 +609,7 @@
           <t>BRENT_CRUDE_USD</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="3" t="n">
         <v>99.06999999999999</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -622,7 +634,7 @@
           <t>JKM_LNG_USD</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -647,7 +659,7 @@
           <t>EU_CARBON_EUR</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n">
+      <c r="B9" s="3" t="n">
         <v>76.09</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -663,6 +675,106 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>2026-05-25 10:59:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>11.491</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-26T07:42:13.429Z</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>98.93000000000001</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-26T08:14:08.306Z</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-24T22:00:05.668Z</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-26T00:07:13.598Z</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-05-26 08:14:37</t>
         </is>
       </c>
     </row>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -778,6 +778,106 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>11.358</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-26T16:42:09.029Z</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:07:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>99.63</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-26T18:06:14.837Z</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:07:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-26T17:06:32.156Z</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:07:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-05-26T00:07:13.598Z</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-05-26 18:07:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -878,6 +878,106 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>11.192</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-05-27T08:42:04.475Z</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:44:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-05-27T08:39:03.346Z</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:44:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>18.42</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-26T17:06:32.156Z</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:44:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-05-27T00:22:12.338Z</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-05-27 08:44:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -978,6 +978,106 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>11.163</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-05-27T16:42:07.620Z</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:08:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>94.79000000000001</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-05-27T18:07:07.635Z</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:08:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-05-27T17:21:30.189Z</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:08:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>77.02</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-27T00:22:12.338Z</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-05-27 18:08:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1078,6 +1078,106 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>11.592</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-28T09:42:06.434Z</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:50:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-05-28T09:50:06.666Z</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-05-27T17:21:30.189Z</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>77.69</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-05-28T00:07:04.692Z</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-05-28 09:50:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1178,6 +1178,106 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>11.219</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-05-29T16:42:09.382Z</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-05-29 18:18:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:12:05.416Z</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-05-29 18:18:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-05-29T17:06:27.699Z</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-05-29 18:18:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-05-29T00:06:54.216Z</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-05-29 18:18:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1278,6 +1278,106 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>11.079</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:42:12.943Z</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-05-30 11:58:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:51:01.776Z</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-05-30 11:58:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-29T17:06:27.699Z</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-05-30 11:58:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>79.12</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-29T00:06:54.216Z</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-05-30 11:58:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1378,6 +1378,106 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>11.079</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-30T01:42:12.943Z</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-05-31 12:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>91.98999999999999</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-05-29T18:51:01.776Z</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-05-31 12:04:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-05-30T22:00:13.742Z</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-05-31 12:04:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>79.59</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-05-30T15:02:16.006Z</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-05-31 12:04:37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1478,6 +1478,106 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-06-01T16:42:07.860Z</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:08:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-06-01T21:07:57.557Z</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:08:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-06-01T17:51:27.552Z</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:08:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-06-01T06:52:13.617Z</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-06-01 21:08:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1578,6 +1578,106 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>11.51</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-06-02T16:42:04.328Z</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:57:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>95.93000000000001</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-06-02T19:57:05.705Z</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:57:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:07:10.977Z</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:57:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>78.13</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-06-02T00:07:06.642Z</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-06-02 19:57:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1678,6 +1678,106 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>11.971</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-06-03T16:42:10.067Z</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-06-03 20:11:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>97.98</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-06-03T20:10:09.489Z</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-06-03 20:11:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-06-03T17:06:26.512Z</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-06-03 20:11:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>78.45</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-06-03T00:07:17.000Z</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-06-03 20:11:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1778,6 +1778,106 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>11.826</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-06-04T16:42:07.408Z</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:49:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>94.44</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-06-04T17:48:04.991Z</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:49:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-06-04T17:21:43.391Z</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:49:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-06-04T00:07:00.411Z</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:49:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1878,6 +1878,106 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>11.766</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:40:15.403Z</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:41:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>92.98999999999999</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-06-05T16:38:22.475Z</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:41:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>18.76</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-06-04T17:21:43.391Z</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:41:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-06-05T00:07:28.923Z</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-06-05 16:41:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1978,6 +1978,106 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>11.705</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:42:05.377Z</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-06-06 12:01:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-06-05T22:15:14.388Z</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-06-06 12:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-06-05T17:51:36.063Z</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-06-06 12:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-06-05T00:07:28.923Z</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-06-06 12:01:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2078,6 +2078,106 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>11.705</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-06-06T01:42:05.377Z</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-06-07 12:15:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>92.78</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-06-05T22:15:14.388Z</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-06-07 12:15:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>18.77</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-06T22:00:16.636Z</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-06-07 12:15:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>76.03</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-06-06T22:00:17.535Z</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-06-07 12:15:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2178,106 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>12.152</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-06-08T16:18:09.199Z</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:09:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>94.15000000000001</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-06-08T18:09:03.906Z</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:09:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>18.89</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-06-08T17:21:26.370Z</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:09:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-06-08T06:22:23.263Z</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-06-08 18:09:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2278,6 +2278,106 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>11.705</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-06-09T15:42:11.501Z</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:10:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-06-09T17:09:07.393Z</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:10:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-06-09T17:06:26.150Z</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:10:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>75.91</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-06-09T00:07:17.671Z</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-06-09 17:10:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2378,6 +2378,106 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>12.21</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-06-10T16:42:11.415Z</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>94.11</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-06-10T18:06:05.977Z</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-06-10T17:06:27.626Z</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>75.13</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-06-10T00:07:00.501Z</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-06-10 18:12:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2478,6 +2478,106 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>11.959</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-06-11T16:42:09.136Z</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-06-11 18:36:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="n">
+        <v>90.26000000000001</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-06-11T18:27:09.956Z</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-06-11 18:36:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>18.92</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-06-11T17:06:40.966Z</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-06-11 18:36:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>76.47</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-06-11T00:06:56.709Z</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-06-11 18:36:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2578,6 +2578,106 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>11.141</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-06-12T16:42:06.454Z</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:28:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>87.19</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:28:42.754Z</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:28:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:21:30.620Z</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:28:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-06-12T00:07:12.963Z</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-06-12 17:28:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2678,6 +2678,106 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>11.191</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:27:08.190Z</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-06-13 13:10:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-06-12T22:15:09.526Z</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-06-13 13:10:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-06-12T17:21:30.620Z</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-06-13 13:10:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>76.12</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-06-12T00:07:12.963Z</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-06-13 13:10:37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2778,6 +2778,31 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>11.191</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-06-13T01:27:08.190Z</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-06-14 13:18:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2803,6 +2803,106 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>10.412</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-01T10:45:10.775Z</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:49:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-07-01T10:45:08.586Z</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:49:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>16.05</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-30T16:51:23.899Z</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:49:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-01T00:22:48.496Z</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-07-01 10:49:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2903,6 +2903,106 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-07-02T09:54:05.645Z</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:14:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-07-02T10:14:34.849Z</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>16.02</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-07-01T17:07:12.649Z</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:14:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>79.54000000000001</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-07-02T00:01:39.454Z</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-07-02 10:14:47</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3003,6 +3003,106 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>10.557</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-07-03T09:51:30.676Z</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:11:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>71.95</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-07-03T10:10:11.685Z</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-07-02T17:06:47.124Z</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:11:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>79.45</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-07-03T00:07:41.285Z</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-07-03 10:11:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3103,6 +3103,106 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>10.764</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-07-04T00:24:25.316Z</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-07-03T23:09:04.518Z</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:31:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-07-03T22:00:15.772Z</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:31:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-07-04T02:43:03.148Z</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-07-04 09:31:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3203,6 +3203,106 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>10.764</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-07-04T00:24:25.316Z</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>72.12</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-07-03T23:09:04.518Z</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-07-04T22:00:34.624Z</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>80.59</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-07-04T02:43:03.148Z</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-07-05 09:47:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3303,6 +3303,106 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>10.649</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-07-06T11:43:41.395Z</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-07-06 11:44:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>71.84</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-07-06T11:42:46.110Z</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-07-06 11:44:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-07-05T22:00:34.870Z</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-07-06 11:44:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-07-06T06:22:30.083Z</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-07-06 11:44:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3403,6 +3403,106 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>10.922</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:27:05.499Z</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-07-07 10:33:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:30:33.519Z</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-07-07 10:33:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-06T17:21:48.493Z</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-07-07 10:33:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-07-07T00:07:13.641Z</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-07-07 10:33:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3503,6 +3503,106 @@
         </is>
       </c>
     </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>11.614</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-07-08T09:18:42.844Z</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:38:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>79.06</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-07-08T09:36:03.021Z</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:38:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-07-07T17:07:08.052Z</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:38:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>80.19</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-07-08T00:09:39.126Z</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2026-07-08 09:38:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3603,6 +3603,106 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>11.665</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-07-09T10:21:07.991Z</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:32:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-07-09T10:30:45.658Z</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:32:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>16.51</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-07-08T17:06:59.756Z</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:32:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>79.04000000000001</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-07-09T00:07:19.169Z</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2026-07-09 10:32:52</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3703,6 +3703,106 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>11.757</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-07-10T10:18:18.767Z</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-07-10T10:27:19.633Z</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-07-09T18:37:18.522Z</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-07-10T06:22:23.230Z</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2026-07-10 10:29:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3803,6 +3803,106 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>11.719</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-07-11T01:21:10.788Z</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:59:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:21:34.200Z</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-07-10T17:22:15.029Z</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:59:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026-07-10T06:22:23.230Z</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2026-07-11 08:59:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3903,6 +3903,106 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>11.719</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026-07-11T13:06:26.019Z</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>75.22</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:21:34.200Z</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:16:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>2026-07-11T22:00:41.893Z</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:16:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2026-07-11T17:32:18.560Z</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>2026-07-12 09:16:34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4003,6 +4003,106 @@
         </is>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-07-13T10:33:15.546Z</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:35:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>78.47</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-13T10:33:27.332Z</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:35:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-12T22:00:25.355Z</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:35:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>78.87</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-13T06:21:06.316Z</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>2026-07-13 10:35:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4103,6 +4103,106 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>12.859</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:16:02.874Z</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:17:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-07-14T09:15:41.863Z</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:17:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-07-13T17:05:40.348Z</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:17:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-07-14T00:01:06.795Z</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>2026-07-14 09:17:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4203,6 +4203,106 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>13.171</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-07-15T09:21:13.796Z</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:22:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>84.93000000000001</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-07-15T09:21:11.267Z</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:22:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026-07-14T17:20:40.438Z</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:22:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>81.39</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026-07-15T00:00:54.431Z</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:22:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4303,6 +4303,106 @@
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026-07-16T09:21:24.701Z</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:28:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>83.97</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026-07-16T09:27:06.867Z</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:28:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2026-07-16T00:01:06.505Z</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:28:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>81.16</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2026-07-16T00:01:13.954Z</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>2026-07-16 09:28:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4403,6 +4403,106 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2026-07-17T09:21:14.650Z</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>85.34</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-07-17T09:21:09.240Z</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:21:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2026-07-17T00:01:05.556Z</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:21:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2026-07-17T00:01:43.652Z</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>2026-07-17 09:21:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4503,6 +4503,106 @@
         </is>
       </c>
     </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>14.219</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2026-07-18T08:56:59.511Z</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:59:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2026-07-18T08:18:44.620Z</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:59:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:01:44.722Z</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:59:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>79.11</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:02:30.708Z</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>2026-07-18 08:59:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E166"/>
+  <dimension ref="A1:E170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4603,6 +4603,106 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>13.875</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2026-07-19T09:15:44.624Z</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:17:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2026-07-19T09:07:49.583Z</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:17:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:01:44.722Z</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:17:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>79.11</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:02:30.708Z</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:17:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E170"/>
+  <dimension ref="A1:E174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4703,6 +4703,106 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>14.019</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:18:33.753Z</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:21:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>88.11</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2026-07-20T10:21:19.279Z</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:21:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>20.98</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2026-07-18T00:01:44.722Z</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:21:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>79.31</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2026-07-20T06:21:26.136Z</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>2026-07-20 10:22:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4803,6 +4803,106 @@
         </is>
       </c>
     </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>14.422</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2026-07-21T09:40:02.066Z</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>2026-07-21 09:40:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2026-07-21T09:39:15.271Z</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>2026-07-21 09:40:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>21.02</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2026-07-20T17:21:16.655Z</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>2026-07-21 09:40:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>83.27</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2026-07-21T00:02:50.703Z</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>2026-07-21 09:40:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -4903,6 +4903,106 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:33:20.093Z</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:39:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>94.69</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2026-07-22T09:39:12.669Z</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:39:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2026-07-21T18:21:00.605Z</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:39:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2026-07-22T00:02:11.649Z</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>2026-07-22 09:39:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5003,6 +5003,106 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2026-07-23T09:33:46.213Z</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>2026-07-23 09:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="n">
+        <v>98.59999999999999</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2026-07-23T09:36:25.405Z</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>2026-07-23 09:37:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2026-07-22T18:01:30.244Z</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>2026-07-23 09:37:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2026-07-23T00:02:44.428Z</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>2026-07-23 09:37:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E186"/>
+  <dimension ref="A1:E187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5103,6 +5103,31 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>15.05</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2026-07-24T09:33:20.289Z</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>2026-07-24 09:35:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E187"/>
+  <dimension ref="A1:E191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5128,6 +5128,106 @@
         </is>
       </c>
     </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2026-07-25T09:12:40.425Z</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>2026-07-25 09:12:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2026-07-25T09:10:28.536Z</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>2026-07-25 09:12:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2026-07-24T18:31:15.510Z</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>2026-07-25 09:12:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2026-07-25T01:41:56.904Z</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>2026-07-25 09:12:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E191"/>
+  <dimension ref="A1:E195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5228,6 +5228,106 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>2026-07-26T09:21:22.499Z</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>2026-07-26 09:24:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B193" s="3" t="n">
+        <v>98.7</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>2026-07-26T08:50:46.287Z</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>2026-07-26 09:24:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>2026-07-24T18:31:15.510Z</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2026-07-26 09:24:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>2026-07-25T01:41:56.904Z</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-07-26 09:24:14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E195"/>
+  <dimension ref="A1:E199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5328,6 +5328,106 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:46:22.269Z</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-07-27 10:50:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B197" s="3" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2026-07-27T10:49:09.299Z</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-07-27 10:50:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B198" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2026-07-24T18:31:15.510Z</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-07-27 10:50:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>83.47</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2026-07-27T06:21:16.472Z</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-07-27 10:50:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E199"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5428,6 +5428,106 @@
         </is>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>13.619</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2026-07-28T09:46:07.594Z</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:48:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n">
+        <v>85.87</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2026-07-28T09:46:18.395Z</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:48:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B202" s="3" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2026-07-27T17:21:27.096Z</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:48:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="n">
+        <v>82.33</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2026-07-28T00:06:39.651Z</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-07-28 09:48:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E203"/>
+  <dimension ref="A1:E207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5528,6 +5528,106 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="n">
+        <v>14.219</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2026-07-29T09:46:23.926Z</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:50:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2026-07-29T09:40:35.800Z</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:50:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2026-07-28T17:21:20.902Z</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:50:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>81.73</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2026-07-29T00:07:09.139Z</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>2026-07-29 09:50:17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E207"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5628,6 +5628,106 @@
         </is>
       </c>
     </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B208" s="3" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2026-08-01T09:08:43.464Z</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2026-08-01T09:16:46.413Z</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B210" s="3" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:06:06.573Z</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B211" s="3" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:06:22.428Z</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-08-01 09:21:32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5728,6 +5728,106 @@
         </is>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:21:37.976Z</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-08-02 09:22:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="n">
+        <v>91.04000000000001</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:16:37.750Z</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>2026-08-02 09:22:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:06:06.573Z</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>2026-08-02 09:22:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B215" s="3" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2026-08-01T00:06:22.428Z</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>2026-08-02 09:22:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E215"/>
+  <dimension ref="A1:E219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5828,6 +5828,106 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:46:29.294Z</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>2026-08-03 10:51:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B217" s="3" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:51:19.803Z</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>2026-08-03 10:51:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="n">
+        <v>21.45</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-07-31T17:06:06.573Z</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>2026-08-03 10:51:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B219" s="3" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:17:01.234Z</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>2026-08-03 10:51:21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E219"/>
+  <dimension ref="A1:E223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -5928,6 +5928,106 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B220" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:58:11.542Z</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>2026-08-04 09:58:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B221" s="3" t="n">
+        <v>86.11</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:58:08.395Z</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>2026-08-04 09:58:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B222" s="3" t="n">
+        <v>21.25</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2026-08-03T17:06:23.869Z</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>2026-08-04 09:58:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="n">
+        <v>80.86</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-08-04T00:01:48.233Z</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>2026-08-04 09:58:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E223"/>
+  <dimension ref="A1:E227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6028,6 +6028,106 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:46:32.983Z</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:49:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="n">
+        <v>80.33</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:49:17.309Z</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:49:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B226" s="3" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-08-04T17:35:53.707Z</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:49:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="n">
+        <v>81.34</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-08-05T00:05:15.935Z</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>2026-08-05 09:49:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E227"/>
+  <dimension ref="A1:E231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6128,6 +6128,106 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:58:29.207Z</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:59:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-08-06T09:55:30.797Z</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:59:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B230" s="3" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:16:18.942Z</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:59:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B231" s="3" t="n">
+        <v>81.09</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-08-06T00:06:45.783Z</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>2026-08-06 09:59:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E231"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6228,6 +6228,106 @@
         </is>
       </c>
     </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:22:09.367Z</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>2026-08-07 08:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B233" s="3" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-08-07T08:31:15.246Z</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>2026-08-07 08:31:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-08-06T17:16:03.933Z</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>2026-08-07 08:31:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:01:56.138Z</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>2026-08-07 08:31:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6328,6 +6328,106 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-08-08T07:57:30.056Z</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>2026-08-08 07:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B237" s="3" t="n">
+        <v>82.20999999999999</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-08-08T07:42:48.377Z</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>2026-08-08 07:59:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-08-07T17:21:19.718Z</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>2026-08-08 07:59:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B239" s="3" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:01:56.138Z</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>2026-08-08 07:59:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E239"/>
+  <dimension ref="A1:E243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6428,6 +6428,106 @@
         </is>
       </c>
     </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-08-09T07:57:01.268Z</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>2026-08-09 08:02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B241" s="3" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>2026-08-09T07:56:14.397Z</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>2026-08-09 08:02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B242" s="3" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>2026-08-07T17:21:19.718Z</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>2026-08-09 08:02:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B243" s="3" t="n">
+        <v>83.29000000000001</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>2026-08-08T15:58:27.492Z</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2026-08-09 08:02:16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6528,6 +6528,106 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B244" s="3" t="n">
+        <v>14.24</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:46:16.241Z</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:51:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="n">
+        <v>84.47</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>2026-08-10T08:51:20.558Z</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:51:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B246" s="3" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>2026-08-07T17:21:19.718Z</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:51:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>2026-08-10T06:21:49.859Z</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>2026-08-10 08:51:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E247"/>
+  <dimension ref="A1:E251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6628,6 +6628,106 @@
         </is>
       </c>
     </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B248" s="3" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:20:47.542Z</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:15:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="n">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-08-11T01:21:22.433Z</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:15:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B250" s="3" t="n">
+        <v>21.26</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-08-10T18:36:03.732Z</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:15:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="n">
+        <v>82.27</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-08-11T00:00:56.735Z</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>2026-08-11 08:15:13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E251"/>
+  <dimension ref="A1:E255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6728,6 +6728,106 @@
         </is>
       </c>
     </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B252" s="3" t="n">
+        <v>14.888</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:39:25.731Z</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>2026-08-12 08:39:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B253" s="3" t="n">
+        <v>89.20999999999999</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:38:21.142Z</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>2026-08-12 08:39:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B254" s="3" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>2026-08-11T17:06:01.079Z</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>2026-08-12 08:39:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B255" s="3" t="n">
+        <v>82.44</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>2026-08-12T02:06:56.503Z</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>2026-08-12 08:39:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E255"/>
+  <dimension ref="A1:E259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6828,6 +6828,106 @@
         </is>
       </c>
     </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="n">
+        <v>14.602</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:40:18.830Z</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:43:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B257" s="3" t="n">
+        <v>87.70999999999999</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>2026-08-13T08:43:17.831Z</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:43:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="n">
+        <v>21.24</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:36:09.016Z</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:43:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B259" s="3" t="n">
+        <v>81.98999999999999</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>2026-08-13T00:06:29.905Z</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>2026-08-13 08:43:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E259"/>
+  <dimension ref="A1:E263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -6928,6 +6928,106 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="n">
+        <v>15.069</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>2026-08-14T08:34:18.505Z</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>2026-08-14 08:38:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B261" s="3" t="n">
+        <v>88.42</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>2026-08-14T08:37:09.771Z</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>2026-08-14 08:38:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:27.327Z</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>2026-08-14 08:38:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B263" s="3" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>2026-08-14T00:05:59.478Z</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>2026-08-14 08:38:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E263"/>
+  <dimension ref="A1:E267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7028,6 +7028,106 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B264" s="3" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:33:47.007Z</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>2026-08-15 07:44:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B265" s="3" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>2026-08-15T07:36:28.630Z</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>2026-08-15 07:44:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B266" s="3" t="n">
+        <v>21.41</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>2026-08-15T00:15:57.211Z</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>2026-08-15 07:44:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>2026-08-15T00:16:24.245Z</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>2026-08-15 07:44:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E267"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7128,6 +7128,106 @@
         </is>
       </c>
     </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B268" s="3" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:44:57.470Z</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>2026-08-16 07:45:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>2026-08-16T07:42:21.731Z</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>2026-08-16 07:45:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B270" s="3" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>2026-08-16T00:01:34.371Z</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>2026-08-16 07:45:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="n">
+        <v>81.79000000000001</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>2026-08-15T00:16:24.245Z</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-08-16 07:45:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:E275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7228,6 +7228,106 @@
         </is>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B272" s="3" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:57:24.814Z</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>2026-08-17T07:55:04.579Z</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B274" s="3" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>2026-08-16T00:01:34.371Z</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B275" s="3" t="n">
+        <v>81.86</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>2026-08-17T06:16:50.996Z</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-08-17 08:00:59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E275"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7328,6 +7328,106 @@
         </is>
       </c>
     </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B276" s="3" t="n">
+        <v>15.419</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>2026-08-18T07:44:56.962Z</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-08-18 07:54:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B277" s="3" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>2026-08-18T07:50:25.652Z</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-08-18 07:54:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>2026-08-17T18:05:58.421Z</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-08-18 07:54:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B279" s="3" t="n">
+        <v>81.58</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>2026-08-18T00:06:20.023Z</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-08-18 07:54:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7428,6 +7428,106 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="n">
+        <v>15.569</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:45:09.973Z</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-08-19 07:54:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B281" s="3" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>2026-08-19T07:50:45.080Z</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-08-19 07:54:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>2026-08-18T18:16:03.865Z</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>2026-08-19 07:54:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B283" s="3" t="n">
+        <v>82.31</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>2026-08-19T00:01:51.226Z</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>2026-08-19 07:54:35</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7528,6 +7528,106 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:56:58.754Z</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:57:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B285" s="3" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>2026-08-20T07:56:14.334Z</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:57:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B286" s="3" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>2026-08-19T18:06:10.571Z</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:57:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B287" s="3" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-08-20T00:02:10.233Z</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>2026-08-20 07:57:37</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E287"/>
+  <dimension ref="A1:E291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7628,6 +7628,106 @@
         </is>
       </c>
     </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B288" s="3" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:56:28.198Z</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:58:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="n">
+        <v>93.34</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>2026-08-21T07:54:16.223Z</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:58:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B290" s="3" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>2026-08-20T17:36:32.349Z</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:58:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>2026-08-21T00:06:45.869Z</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>2026-08-21 07:58:05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E291"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7728,6 +7728,106 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B292" s="3" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:44:56.987Z</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>2026-08-22 07:46:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>2026-08-22T07:41:18.750Z</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>2026-08-22 07:46:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B294" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:06:05.391Z</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2026-08-22 07:46:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>2026-08-22T00:16:35.858Z</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>2026-08-22 07:46:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E295"/>
+  <dimension ref="A1:E299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7828,6 +7828,106 @@
         </is>
       </c>
     </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B296" s="3" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:44:52.286Z</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:47:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B297" s="3" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>2026-08-23T07:36:17.853Z</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:47:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B298" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:06:05.391Z</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:47:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B299" s="3" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>2026-08-22T00:16:35.858Z</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>2026-08-23 07:47:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E299"/>
+  <dimension ref="A1:E303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -7928,6 +7928,106 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:01:26.624Z</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>2026-08-24 08:04:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B301" s="3" t="n">
+        <v>93.13</v>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>2026-08-24T08:02:47.320Z</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>2026-08-24 08:04:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>2026-08-21T18:06:05.391Z</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>2026-08-24 08:04:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B303" s="3" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>2026-08-24T06:21:25.157Z</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>2026-08-24 08:04:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E303"/>
+  <dimension ref="A1:E307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8028,6 +8028,106 @@
         </is>
       </c>
     </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:57:59.950Z</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>2026-08-25 07:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B305" s="3" t="n">
+        <v>91.51000000000001</v>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>2026-08-25T07:57:24.440Z</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>2026-08-25 07:59:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="n">
+        <v>23.51</v>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>2026-08-24T17:21:10.350Z</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>2026-08-25 07:59:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B307" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>2026-08-25T00:01:34.838Z</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>2026-08-25 07:59:11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E307"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8128,6 +8128,106 @@
         </is>
       </c>
     </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B308" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>2026-08-26T07:57:55.730Z</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>2026-08-26 08:00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B309" s="3" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>2026-08-26T07:56:33.733Z</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>2026-08-26 08:00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B310" s="3" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-08-25T17:21:02.850Z</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>2026-08-26 08:00:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-08-26T00:52:24.043Z</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>2026-08-26 08:00:20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8228,6 +8228,106 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B312" s="3" t="n">
+        <v>16.968</v>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>2026-08-27T18:16:10.386Z</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:17:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="n">
+        <v>90.06</v>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-08-27T18:16:20.168Z</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:17:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B314" s="3" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-08-27T17:51:04.216Z</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:17:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-08-27T00:02:16.099Z</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>2026-08-27 18:17:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8328,6 +8328,106 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B316" s="3" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-08-28T19:21:32.192Z</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-08-28T19:21:16.724Z</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B318" s="3" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-08-28T18:06:13.317Z</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:26:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B319" s="3" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-08-28T00:06:55.802Z</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>2026-08-28 19:26:57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E319"/>
+  <dimension ref="A1:E323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8428,6 +8428,106 @@
         </is>
       </c>
     </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B320" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:09:57.934Z</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>2026-08-29 13:10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B321" s="3" t="n">
+        <v>88.28</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-08-29T13:07:20.391Z</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>2026-08-29 13:10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-08-28T18:06:13.317Z</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>2026-08-29 13:10:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B323" s="3" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-08-28T00:06:55.802Z</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>2026-08-29 13:10:18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E323"/>
+  <dimension ref="A1:E327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8528,6 +8528,106 @@
         </is>
       </c>
     </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:45:30.504Z</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>2026-08-30 12:55:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B325" s="3" t="n">
+        <v>88.28</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>2026-08-30T12:54:48.576Z</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>2026-08-30 12:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>2026-08-28T18:06:13.317Z</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>2026-08-30 12:55:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B327" s="3" t="n">
+        <v>82.73</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>2026-08-29T15:58:40.901Z</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>2026-08-30 12:55:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E327"/>
+  <dimension ref="A1:E331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8628,6 +8628,106 @@
         </is>
       </c>
     </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>2026-08-31T14:57:21.135Z</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:06:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B329" s="3" t="n">
+        <v>90.39</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>2026-08-31T15:06:18.813Z</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:06:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B330" s="3" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>2026-08-28T18:06:13.317Z</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:06:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B331" s="3" t="n">
+        <v>82.79000000000001</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>2026-08-31T06:21:30.828Z</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>2026-08-31 15:06:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E331"/>
+  <dimension ref="A1:E335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8728,6 +8728,106 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B332" s="3" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>2026-09-01T12:34:30.750Z</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="n">
+        <v>92.13</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>2026-09-01T12:34:26.579Z</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:34:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B334" s="3" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>2026-08-31T18:36:14.099Z</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:34:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>2026-09-01T00:06:40.473Z</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>2026-09-01 12:34:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E335"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8828,6 +8828,106 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B336" s="3" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>2026-09-02T11:58:16.730Z</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:07:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>2026-09-02T12:07:07.467Z</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:07:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B338" s="3" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>2026-09-01T18:16:08.269Z</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:07:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="n">
+        <v>83.34</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>2026-09-02T00:06:51.063Z</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>2026-09-02 12:07:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E339"/>
+  <dimension ref="A1:E343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -8928,6 +8928,106 @@
         </is>
       </c>
     </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B340" s="3" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>2026-09-03T11:58:19.139Z</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:06:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B341" s="3" t="n">
+        <v>97.13</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>2026-09-03T12:05:23.770Z</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B342" s="3" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>2026-09-02T18:21:30.983Z</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:06:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B343" s="3" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>2026-09-03T00:06:51.341Z</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>2026-09-03 12:06:28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E343"/>
+  <dimension ref="A1:E347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9028,6 +9028,106 @@
         </is>
       </c>
     </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="n">
+        <v>17.594</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>2026-09-04T11:40:06.776Z</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:08:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B345" s="3" t="n">
+        <v>95.09</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:07:18.166Z</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:08:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>2026-09-02T18:21:30.983Z</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:08:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B347" s="3" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>2026-09-03T00:06:51.341Z</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>2026-09-04 12:08:08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E347"/>
+  <dimension ref="A1:E351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9128,6 +9128,106 @@
         </is>
       </c>
     </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="n">
+        <v>17.881</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>2026-09-05T10:15:19.831Z</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B349" s="3" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>2026-09-05T11:06:50.221Z</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:10.258Z</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:16:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B351" s="3" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:42.864Z</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>2026-09-05 11:16:31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
